--- a/TestCase_Logic_วินิจฉัยว่างงาน_BA.xlsx
+++ b/TestCase_Logic_วินิจฉัยว่างงาน_BA.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1108,6 +1108,58 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>TC-11</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>[137] เคยเรียกเงินคืน → คืนสิทธิ</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>ลาออก</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>กฎ 2568 · 30%</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>สะสมก่อนหน้า 55 · เรียกเงินคืน 50</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>วันใช้สุทธิ = 55-50 = 5 → สิทธิที่วินิจฉัยได้ = 90-5 = 85 วัน</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>ตามจริง</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>ก่อนแก้ระบบให้ 35 (หักวันเรียกคืนผิด) · หลังแก้ = 85</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
@@ -1123,7 +1175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1369,6 +1421,23 @@
       <c r="C16" s="8" t="inlineStr">
         <is>
           <t>กฎกระทรวง 2547 = ค่าตั้งต้น · ช่วงที่ไม่มีประกาศเฉพาะใช้ค่านี้อัตโนมัติ (ไม่มีแนวคิดช่องว่าง)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>การเรียกเงินคืน = คืนสิทธิ [137]</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>วันที่เคยถูกเรียกเงินคืน ต้องคืนสิทธิ ไม่นับเป็นวันใช้สิทธิ → วันใช้สิทธิสุทธิ = วันใช้สะสมก่อนหน้า − วันที่เรียกเงินคืน ; ป้องกันระบบคำนวณสิทธิขาด (เช่น ควรได้ 85 แต่ระบบหัก 50 ที่เรียกคืนไปด้วยจนเหลือ 35)</t>
         </is>
       </c>
     </row>
